--- a/alphabet/model.xlsx
+++ b/alphabet/model.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:H44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -1140,11 +1140,21 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
+          <t>Preferred stock</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="n">
+        <v>18023000000</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
           <t>Spot price</t>
         </is>
       </c>
-      <c r="B43" s="10" t="n">
-        <v>377.65</v>
+      <c r="B44" s="10" t="n">
+        <v>357.94</v>
       </c>
     </row>
   </sheetData>
@@ -1671,7 +1681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -2253,77 +2263,88 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>Equity value</t>
+          <t>- Preferred stock</t>
         </is>
       </c>
       <c r="B27" s="11">
-        <f>B22+B23+B24+B25+B26</f>
+        <f>-Drivers!$B$43</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>Value per share</t>
-        </is>
-      </c>
-      <c r="B28" s="18">
-        <f>B27/Drivers!$B$38</f>
+          <t>Equity value</t>
+        </is>
+      </c>
+      <c r="B28" s="11">
+        <f>B22+B23+B24+B25+B26+B27</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>Spot price</t>
-        </is>
-      </c>
-      <c r="B29" s="19">
-        <f>Drivers!$B$43</f>
+          <t>Value per share</t>
+        </is>
+      </c>
+      <c r="B29" s="18">
+        <f>B28/Drivers!$B$38</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>Upside / (downside)</t>
-        </is>
-      </c>
-      <c r="B30" s="13">
-        <f>B28/B29-1</f>
+          <t>Spot price</t>
+        </is>
+      </c>
+      <c r="B30" s="19">
+        <f>Drivers!$B$44</f>
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
+          <t>Upside / (downside)</t>
+        </is>
+      </c>
+      <c r="B31" s="13">
+        <f>B29/B30-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
           <t>Terminal value % of EV</t>
         </is>
       </c>
-      <c r="B31" s="13">
+      <c r="B32" s="13">
         <f>B21/B22</f>
         <v/>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>Sanity check: WACC minus terminal growth should exceed 150bp.</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>WACC - g</t>
         </is>
       </c>
-      <c r="B34" s="20">
+      <c r="B35" s="20">
         <f>Drivers!$B$36-Drivers!$B$37</f>
         <v/>
       </c>
-      <c r="C34">
-        <f>IF(B34&gt;0.015,"OK","FAIL — terminal value unstable")</f>
+      <c r="C35">
+        <f>IF(B35&gt;0.015,"OK","FAIL — terminal value unstable")</f>
         <v/>
       </c>
     </row>
@@ -2609,13 +2630,13 @@
         </is>
       </c>
       <c r="B4" s="19" t="n">
-        <v>114.7266842997515</v>
+        <v>113.2624711224016</v>
       </c>
       <c r="C4" s="13" t="n">
         <v>0.25</v>
       </c>
       <c r="D4" s="13">
-        <f>B4/Valuation!B29-1</f>
+        <f>B4/Valuation!B30-1</f>
         <v/>
       </c>
       <c r="E4" t="inlineStr">
@@ -2631,13 +2652,13 @@
         </is>
       </c>
       <c r="B5" s="19" t="n">
-        <v>195.6503291117316</v>
+        <v>194.1861159343817</v>
       </c>
       <c r="C5" s="13" t="n">
         <v>0.45</v>
       </c>
       <c r="D5" s="13">
-        <f>B5/Valuation!B29-1</f>
+        <f>B5/Valuation!B30-1</f>
         <v/>
       </c>
       <c r="E5" t="inlineStr">
@@ -2653,13 +2674,13 @@
         </is>
       </c>
       <c r="B6" s="19" t="n">
-        <v>439.3087451390608</v>
+        <v>437.8445319617109</v>
       </c>
       <c r="C6" s="13" t="n">
         <v>0.3</v>
       </c>
       <c r="D6" s="13">
-        <f>B6/Valuation!B29-1</f>
+        <f>B6/Valuation!B30-1</f>
         <v/>
       </c>
       <c r="E6" t="inlineStr">
@@ -2683,7 +2704,7 @@
         <v/>
       </c>
       <c r="D7" s="13">
-        <f>B7/Valuation!B29-1</f>
+        <f>B7/Valuation!B30-1</f>
         <v/>
       </c>
     </row>
@@ -2706,7 +2727,7 @@
         </is>
       </c>
       <c r="B10" s="22" t="n">
-        <v>2.094318607876743</v>
+        <v>1.387746949241255</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
@@ -2721,7 +2742,7 @@
         </is>
       </c>
       <c r="B11" s="22" t="n">
-        <v>2.094318607876743</v>
+        <v>1.387746949241255</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
@@ -2751,7 +2772,7 @@
         </is>
       </c>
       <c r="B13" s="13" t="n">
-        <v>0.5567553194286204</v>
+        <v>0.4838222594082993</v>
       </c>
       <c r="E13" s="2" t="inlineStr"/>
     </row>
@@ -2762,7 +2783,7 @@
         </is>
       </c>
       <c r="B14" s="13" t="n">
-        <v>0.1391888298571551</v>
+        <v>0.1209555648520748</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
@@ -2792,7 +2813,7 @@
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>0.09187261250977655</v>
+        <v>0.06719393591558484</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>

--- a/alphabet/model.xlsx
+++ b/alphabet/model.xlsx
@@ -920,19 +920,19 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>0.295</v>
+        <v>0.3464596359223742</v>
       </c>
       <c r="C24" s="6" t="n">
-        <v>0.27</v>
+        <v>0.3111677087378994</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>0.24</v>
+        <v>0.2688173961165296</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>0.21</v>
+        <v>0.2264670834951597</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>0.185</v>
+        <v>0.1911751563106849</v>
       </c>
       <c r="G24" s="6" t="n">
         <v>0.17</v>
@@ -1585,22 +1585,22 @@
         </is>
       </c>
       <c r="B6" s="14" t="n">
-        <v>39998265854.076</v>
+        <v>41659017600.00001</v>
       </c>
       <c r="C6" s="14" t="n">
-        <v>56638990747.88184</v>
+        <v>61496235646.29254</v>
       </c>
       <c r="D6" s="14" t="n">
-        <v>73081354671.9088</v>
+        <v>80693094084.26115</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>89289549095.0303</v>
+        <v>98899016963.33727</v>
       </c>
       <c r="F6" s="14" t="n">
-        <v>102608877619.3317</v>
+        <v>113320607926.203</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>111064582646.3764</v>
+        <v>122099600043.2363</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="B4" s="19" t="n">
-        <v>113.2624711224016</v>
+        <v>109.7568203976805</v>
       </c>
       <c r="C4" s="13" t="n">
         <v>0.25</v>
@@ -2652,7 +2652,7 @@
         </is>
       </c>
       <c r="B5" s="19" t="n">
-        <v>194.1861159343817</v>
+        <v>190.759460824556</v>
       </c>
       <c r="C5" s="13" t="n">
         <v>0.45</v>
@@ -2674,7 +2674,7 @@
         </is>
       </c>
       <c r="B6" s="19" t="n">
-        <v>437.8445319617109</v>
+        <v>435.5833961765223</v>
       </c>
       <c r="C6" s="13" t="n">
         <v>0.3</v>
@@ -2727,7 +2727,7 @@
         </is>
       </c>
       <c r="B10" s="22" t="n">
-        <v>1.387746949241255</v>
+        <v>1.46804524646797</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
@@ -2742,7 +2742,7 @@
         </is>
       </c>
       <c r="B11" s="22" t="n">
-        <v>1.387746949241255</v>
+        <v>1.46804524646797</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
@@ -2772,7 +2772,7 @@
         </is>
       </c>
       <c r="B13" s="13" t="n">
-        <v>0.4838222594082993</v>
+        <v>0.4956466255234419</v>
       </c>
       <c r="E13" s="2" t="inlineStr"/>
     </row>
@@ -2783,7 +2783,7 @@
         </is>
       </c>
       <c r="B14" s="13" t="n">
-        <v>0.1209555648520748</v>
+        <v>0.1239116563808605</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>0.06719393591558484</v>
+        <v>0.06915076187282361</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>

--- a/alphabet/model.xlsx
+++ b/alphabet/model.xlsx
@@ -920,19 +920,19 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>0.3464596359223742</v>
+        <v>0.406533020337672</v>
       </c>
       <c r="C24" s="6" t="n">
-        <v>0.3111677087378994</v>
+        <v>0.3592264162701376</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>0.2688173961165296</v>
+        <v>0.3024584913890963</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>0.2264670834951597</v>
+        <v>0.245690566508055</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>0.1911751563106849</v>
+        <v>0.1983839624405206</v>
       </c>
       <c r="G24" s="6" t="n">
         <v>0.17</v>
@@ -1104,7 +1104,7 @@
         </is>
       </c>
       <c r="B39" s="7" t="n">
-        <v>242474000000</v>
+        <v>267274000000</v>
       </c>
     </row>
     <row r="40">
@@ -1124,7 +1124,7 @@
         </is>
       </c>
       <c r="B41" s="7" t="n">
-        <v>100164000000</v>
+        <v>125164000000</v>
       </c>
     </row>
     <row r="42">
@@ -1154,7 +1154,7 @@
         </is>
       </c>
       <c r="B44" s="10" t="n">
-        <v>357.94</v>
+        <v>354.24</v>
       </c>
     </row>
   </sheetData>
@@ -1585,22 +1585,22 @@
         </is>
       </c>
       <c r="B6" s="14" t="n">
-        <v>41659017600.00001</v>
+        <v>43597760000</v>
       </c>
       <c r="C6" s="14" t="n">
-        <v>61496235646.29254</v>
+        <v>67166527220.4815</v>
       </c>
       <c r="D6" s="14" t="n">
-        <v>80693094084.26115</v>
+        <v>89578950728.81819</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>98899016963.33727</v>
+        <v>110116998725.7823</v>
       </c>
       <c r="F6" s="14" t="n">
-        <v>113320607926.203</v>
+        <v>125825358123.9767</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>122099600043.2363</v>
+        <v>134981751854.6299</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Street figures are the consensus feed as retrieved 2026-08-05. Low/high are the support of published estimates, not a confidence interval.</t>
+          <t>Street figures are the consensus feed as retrieved 2026-08-07. Low/high are the support of published estimates, not a confidence interval.</t>
         </is>
       </c>
     </row>
@@ -2436,19 +2436,19 @@
         <v>491964957320.9999</v>
       </c>
       <c r="C5" s="11" t="n">
-        <v>495194912007</v>
+        <v>495359381557</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>488834946807</v>
+        <v>488997304016</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>500626666069</v>
+        <v>500792939672</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>-0.00652259263510846</v>
+        <v>-0.006852447662000105</v>
       </c>
       <c r="G5" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -2464,16 +2464,16 @@
         <v>568666386615.281</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>605866802904</v>
+        <v>606613875390</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>574063447987</v>
+        <v>574771304904</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>653723173062</v>
+        <v>654529255511</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>-0.06140032117688654</v>
+        <v>-0.06255624922908676</v>
       </c>
       <c r="G6" t="n">
         <v>39</v>
@@ -2492,19 +2492,19 @@
         <v>644699243159.1138</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>721625171799</v>
+        <v>721625172376</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>539933823678</v>
+        <v>538737786017</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>798798263142</v>
+        <v>797028800359</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>-0.1066009496981807</v>
+        <v>-0.1066009504125284</v>
       </c>
       <c r="G7" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -2523,16 +2523,16 @@
         <v>815730364847</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>714927001762</v>
+        <v>714345859869</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>879702248650</v>
+        <v>878987166090</v>
       </c>
       <c r="F8" s="13" t="n">
         <v>-0.1159912607439061</v>
       </c>
       <c r="G8" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -2551,16 +2551,16 @@
         <v>936258242857</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>820560723599</v>
+        <v>819893715344</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>1009682263958</v>
+        <v>1008861524693</v>
       </c>
       <c r="F9" s="13" t="n">
         <v>-0.147604961669581</v>
       </c>
       <c r="G9" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="B4" s="19" t="n">
-        <v>109.7568203976805</v>
+        <v>105.4827056898842</v>
       </c>
       <c r="C4" s="13" t="n">
         <v>0.25</v>
@@ -2652,7 +2652,7 @@
         </is>
       </c>
       <c r="B5" s="19" t="n">
-        <v>190.759460824556</v>
+        <v>186.742974967021</v>
       </c>
       <c r="C5" s="13" t="n">
         <v>0.45</v>
@@ -2674,7 +2674,7 @@
         </is>
       </c>
       <c r="B6" s="19" t="n">
-        <v>435.5833961765223</v>
+        <v>433.1807537628952</v>
       </c>
       <c r="C6" s="13" t="n">
         <v>0.3</v>
@@ -2727,7 +2727,7 @@
         </is>
       </c>
       <c r="B10" s="22" t="n">
-        <v>1.46804524646797</v>
+        <v>1.442610480456658</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
@@ -2742,7 +2742,7 @@
         </is>
       </c>
       <c r="B11" s="22" t="n">
-        <v>1.46804524646797</v>
+        <v>1.442610480456658</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
@@ -2772,7 +2772,7 @@
         </is>
       </c>
       <c r="B13" s="13" t="n">
-        <v>0.4956466255234419</v>
+        <v>0.4920436569232222</v>
       </c>
       <c r="E13" s="2" t="inlineStr"/>
     </row>
@@ -2783,7 +2783,7 @@
         </is>
       </c>
       <c r="B14" s="13" t="n">
-        <v>0.1239116563808605</v>
+        <v>0.1230109142308056</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         </is>
       </c>
       <c r="B15" s="13" t="n">
-        <v>22.4</v>
+        <v>11.96</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>0.06915076187282361</v>
+        <v>0.06731123971731789</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -2899,7 +2899,7 @@
     <row r="5">
       <c r="A5" s="24" t="inlineStr">
         <is>
-          <t>Consensus estimates and price targets: FMP analyst/financial-estimates and analyst/price-target-consensus, retrieved 2026-08-05.</t>
+          <t>Consensus estimates and price targets: FMP analyst/financial-estimates and analyst/price-target-consensus, retrieved 2026-08-07.</t>
         </is>
       </c>
     </row>
@@ -2916,7 +2916,7 @@
     <row r="8">
       <c r="A8" s="24" t="inlineStr">
         <is>
-          <t>MODEL DESIGN. We forecast EBITDA margin and derive EBIT by subtracting a depreciation schedule built from capex vintages. Forecasting EBIT margin directly hides the depreciation assumption.</t>
+          <t>YEAR-1 CAPEX ANCHOR. Management guided full-year capex to $195-205bn (Q2 2026 earnings call, 22 July 2026 (CFO Anat Ashkenazi)); the base case takes the midpoint, $200.0bn, against $80.6bn already reported. Holding the exit quarter flat instead would give $170.4bn, below the guided range. Guidance outranks extrapolation for a period management has guided.</t>
         </is>
       </c>
     </row>
@@ -2926,7 +2926,7 @@
     <row r="10">
       <c r="A10" s="24" t="inlineStr">
         <is>
-          <t>KEY LIMITATION. The asset-life split driving the depreciation schedule is a stated assumption calibrated to reported D&amp;A, not a disclosed figure. It is the most load-bearing assumption in the model.</t>
+          <t>MODEL DESIGN. We forecast EBITDA margin and derive EBIT by subtracting a depreciation schedule built from capex vintages. Forecasting EBIT margin directly hides the depreciation assumption.</t>
         </is>
       </c>
     </row>
@@ -2935,6 +2935,16 @@
     </row>
     <row r="12">
       <c r="A12" s="24" t="inlineStr">
+        <is>
+          <t>KEY LIMITATION. The asset-life split driving the depreciation schedule is a stated assumption calibrated to reported D&amp;A, not a disclosed figure. It is the most load-bearing assumption in the model.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="24" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="24" t="inlineStr">
         <is>
           <t>This is analytical research on public information. Not investment advice, not a recommendation to any person, and not a solicitation. Position sizing is illustrative against a notional $1bn book.</t>
         </is>

--- a/alphabet/model.xlsx
+++ b/alphabet/model.xlsx
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>0.55</v>
+        <v>0.66</v>
       </c>
       <c r="C19" s="6" t="n">
         <v>0.34</v>
@@ -920,19 +920,19 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>0.406533020337672</v>
+        <v>0.4012659883178061</v>
       </c>
       <c r="C24" s="6" t="n">
-        <v>0.3592264162701376</v>
+        <v>0.355012790654245</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>0.3024584913890963</v>
+        <v>0.2995089534579714</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>0.245690566508055</v>
+        <v>0.244005116261698</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>0.1983839624405206</v>
+        <v>0.1977519185981367</v>
       </c>
       <c r="G24" s="6" t="n">
         <v>0.17</v>
@@ -1588,19 +1588,19 @@
         <v>43597760000</v>
       </c>
       <c r="C6" s="14" t="n">
-        <v>67166527220.4815</v>
+        <v>67210861009.88953</v>
       </c>
       <c r="D6" s="14" t="n">
-        <v>89578950728.81819</v>
+        <v>89760494343.50021</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>110116998725.7823</v>
+        <v>110529755397.1962</v>
       </c>
       <c r="F6" s="14" t="n">
-        <v>125825358123.9767</v>
+        <v>126553672145.8761</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>134981751854.6299</v>
+        <v>136095200917.4288</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>2026</v>
       </c>
       <c r="B5" s="11" t="n">
-        <v>491964957320.9999</v>
+        <v>498422507320.9999</v>
       </c>
       <c r="C5" s="11" t="n">
         <v>495359381557</v>
@@ -2445,7 +2445,7 @@
         <v>500792939672</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>-0.006852447662000105</v>
+        <v>0.006183643387094095</v>
       </c>
       <c r="G5" t="n">
         <v>36</v>
@@ -2461,7 +2461,7 @@
         <v>2027</v>
       </c>
       <c r="B6" s="11" t="n">
-        <v>568666386615.281</v>
+        <v>577319503615.2811</v>
       </c>
       <c r="C6" s="11" t="n">
         <v>606613875390</v>
@@ -2473,14 +2473,14 @@
         <v>654529255511</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>-0.06255624922908676</v>
+        <v>-0.04829162827158406</v>
       </c>
       <c r="G6" t="n">
         <v>39</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>OUTSIDE</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -2489,7 +2489,7 @@
         <v>2028</v>
       </c>
       <c r="B7" s="11" t="n">
-        <v>644699243159.1138</v>
+        <v>655775232919.1138</v>
       </c>
       <c r="C7" s="11" t="n">
         <v>721625172376</v>
@@ -2501,7 +2501,7 @@
         <v>797028800359</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>-0.1066009504125284</v>
+        <v>-0.09125227608132191</v>
       </c>
       <c r="G7" t="n">
         <v>37</v>
@@ -2517,7 +2517,7 @@
         <v>2029</v>
       </c>
       <c r="B8" s="11" t="n">
-        <v>721112771401.3099</v>
+        <v>734736238806.11</v>
       </c>
       <c r="C8" s="11" t="n">
         <v>815730364847</v>
@@ -2529,7 +2529,7 @@
         <v>878987166090</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>-0.1159912607439061</v>
+        <v>-0.09929031642224262</v>
       </c>
       <c r="G8" t="n">
         <v>23</v>
@@ -2545,7 +2545,7 @@
         <v>2030</v>
       </c>
       <c r="B9" s="11" t="n">
-        <v>798061880807.2632</v>
+        <v>814273807018.9752</v>
       </c>
       <c r="C9" s="11" t="n">
         <v>936258242857</v>
@@ -2557,7 +2557,7 @@
         <v>1008861524693</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>-0.147604961669581</v>
+        <v>-0.1302893050808164</v>
       </c>
       <c r="G9" t="n">
         <v>33</v>
@@ -2630,7 +2630,7 @@
         </is>
       </c>
       <c r="B4" s="19" t="n">
-        <v>105.4827056898842</v>
+        <v>107.5024971522942</v>
       </c>
       <c r="C4" s="13" t="n">
         <v>0.25</v>
@@ -2652,7 +2652,7 @@
         </is>
       </c>
       <c r="B5" s="19" t="n">
-        <v>186.742974967021</v>
+        <v>190.5122756643074</v>
       </c>
       <c r="C5" s="13" t="n">
         <v>0.45</v>
@@ -2674,7 +2674,7 @@
         </is>
       </c>
       <c r="B6" s="19" t="n">
-        <v>433.1807537628952</v>
+        <v>442.5312481864872</v>
       </c>
       <c r="C6" s="13" t="n">
         <v>0.3</v>
@@ -2727,7 +2727,7 @@
         </is>
       </c>
       <c r="B10" s="22" t="n">
-        <v>1.442610480456658</v>
+        <v>1.233128757870534</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
@@ -2742,7 +2742,7 @@
         </is>
       </c>
       <c r="B11" s="22" t="n">
-        <v>1.442610480456658</v>
+        <v>1.233128757870534</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
@@ -2772,7 +2772,7 @@
         </is>
       </c>
       <c r="B13" s="13" t="n">
-        <v>0.4920436569232222</v>
+        <v>0.4567164028206883</v>
       </c>
       <c r="E13" s="2" t="inlineStr"/>
     </row>
@@ -2783,7 +2783,7 @@
         </is>
       </c>
       <c r="B14" s="13" t="n">
-        <v>0.1230109142308056</v>
+        <v>0.1141791007051721</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>0.06731123971731789</v>
+        <v>0.0601826354156497</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A14"/>
+  <dimension ref="A1:A18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -2926,7 +2926,7 @@
     <row r="10">
       <c r="A10" s="24" t="inlineStr">
         <is>
-          <t>MODEL DESIGN. We forecast EBITDA margin and derive EBIT by subtracting a depreciation schedule built from capex vintages. Forecasting EBIT margin directly hides the depreciation assumption.</t>
+          <t>YEAR-1 SEGMENT ANCHOR. Each segment's year-1 forecast is checked against its own reported quarters: the stub implied for the 2 remaining quarter(s) may not sit more than 2% below the exit quarter. The tightest is network at +0.1%. This exists because a consolidated total can be right while the mix inside it is wrong: the prior edition forecast Cloud below its own exit rate and nothing consolidated could see it.</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
     <row r="12">
       <c r="A12" s="24" t="inlineStr">
         <is>
-          <t>KEY LIMITATION. The asset-life split driving the depreciation schedule is a stated assumption calibrated to reported D&amp;A, not a disclosed figure. It is the most load-bearing assumption in the model.</t>
+          <t>DISCOUNT RATE. WACC is an input cell on Drivers and every discounted line references it, so changing it here re-values the model. It is worth knowing what that is worth: terminal value is 89% of enterprise value, the base case discounts at 8.75% giving $190.51, published third-party WACC estimates cluster near 7.57% giving $243.01, and the reverse DCF implies the market is discounting at 6.19%. The discount rate moves this valuation more than the depreciation schedule does.</t>
         </is>
       </c>
     </row>
@@ -2945,6 +2945,26 @@
     </row>
     <row r="14">
       <c r="A14" s="24" t="inlineStr">
+        <is>
+          <t>MODEL DESIGN. We forecast EBITDA margin and derive EBIT by subtracting a depreciation schedule built from capex vintages. Forecasting EBIT margin directly hides the depreciation assumption.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="24" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="24" t="inlineStr">
+        <is>
+          <t>KEY LIMITATION. The asset-life split driving the depreciation schedule is a stated assumption calibrated to reported D&amp;A, not a disclosed figure. It is the most load-bearing assumption in the model.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="24" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="24" t="inlineStr">
         <is>
           <t>This is analytical research on public information. Not investment advice, not a recommendation to any person, and not a solicitation. Position sizing is illustrative against a notional $1bn book.</t>
         </is>
